--- a/budgetdirect-2026.xlsx
+++ b/budgetdirect-2026.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D833168A-A8B1-4E92-8787-273486864ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21C08C5-3406-48FF-B4E4-FE868E1BAC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget2026" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -89,7 +102,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -115,13 +139,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -459,8 +487,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="14" width="14.83203125" customWidth="1"/>
@@ -468,7 +496,7 @@
     <col min="16" max="16" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -518,110 +546,140 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2">
-        <v>300</v>
-      </c>
-      <c r="D2">
-        <v>300</v>
-      </c>
-      <c r="E2">
-        <v>300</v>
-      </c>
-      <c r="F2">
-        <v>300</v>
-      </c>
-      <c r="G2">
-        <v>300</v>
-      </c>
-      <c r="H2">
-        <v>300</v>
-      </c>
-      <c r="I2">
-        <v>300</v>
-      </c>
-      <c r="J2">
-        <v>300</v>
-      </c>
-      <c r="K2">
-        <v>300</v>
-      </c>
-      <c r="L2">
-        <v>300</v>
-      </c>
-      <c r="M2">
-        <v>300</v>
-      </c>
-      <c r="N2">
-        <v>300</v>
-      </c>
-      <c r="O2">
-        <v>3600</v>
+      <c r="C2" s="2">
+        <v>192.26</v>
+      </c>
+      <c r="D2" s="2">
+        <v>192.26</v>
+      </c>
+      <c r="E2" s="2">
+        <v>213.58</v>
+      </c>
+      <c r="F2" s="2">
+        <v>187.42</v>
+      </c>
+      <c r="G2" s="2">
+        <v>138.85</v>
+      </c>
+      <c r="H2" s="2">
+        <v>218.96</v>
+      </c>
+      <c r="I2" s="2">
+        <v>197.6</v>
+      </c>
+      <c r="J2" s="2">
+        <v>106.81</v>
+      </c>
+      <c r="K2" s="2">
+        <v>229.64</v>
+      </c>
+      <c r="L2" s="2">
+        <v>218.96</v>
+      </c>
+      <c r="M2" s="2">
+        <v>197.6</v>
+      </c>
+      <c r="N2" s="2">
+        <v>181.58</v>
+      </c>
+      <c r="O2" s="2">
+        <f>+SUM(C2:N2)</f>
+        <v>2275.5199999999995</v>
       </c>
       <c r="P2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="C3">
-        <v>250</v>
-      </c>
-      <c r="D3">
-        <v>250</v>
-      </c>
-      <c r="E3">
-        <v>250</v>
-      </c>
-      <c r="F3">
-        <v>250</v>
-      </c>
-      <c r="G3">
-        <v>250</v>
-      </c>
-      <c r="H3">
-        <v>250</v>
-      </c>
-      <c r="I3">
-        <v>250</v>
-      </c>
-      <c r="J3">
-        <v>250</v>
-      </c>
-      <c r="K3">
-        <v>250</v>
-      </c>
-      <c r="L3">
-        <v>250</v>
-      </c>
-      <c r="M3">
-        <v>250</v>
-      </c>
-      <c r="N3">
-        <v>250</v>
-      </c>
-      <c r="O3">
-        <v>3000</v>
+      <c r="C3" s="2">
+        <v>192.26</v>
+      </c>
+      <c r="D3" s="2">
+        <v>192.26</v>
+      </c>
+      <c r="E3" s="2">
+        <v>213.58</v>
+      </c>
+      <c r="F3" s="2">
+        <v>187.42</v>
+      </c>
+      <c r="G3" s="2">
+        <v>138.85</v>
+      </c>
+      <c r="H3" s="2">
+        <v>218.96</v>
+      </c>
+      <c r="I3" s="2">
+        <v>197.6</v>
+      </c>
+      <c r="J3" s="2">
+        <v>106.81</v>
+      </c>
+      <c r="K3" s="2">
+        <v>229.64</v>
+      </c>
+      <c r="L3" s="2">
+        <v>218.96</v>
+      </c>
+      <c r="M3" s="2">
+        <v>197.6</v>
+      </c>
+      <c r="N3" s="2">
+        <v>181.58</v>
+      </c>
+      <c r="O3" s="2">
+        <f>+SUM(C3:N3)</f>
+        <v>2275.5199999999995</v>
       </c>
       <c r="P3" t="s">
         <v>18</v>
       </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P1 A3:B3 A2:B2 P2 P3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>